--- a/tests/traces/compare_test_e2e/reference/h100_perf_report.xlsx
+++ b/tests/traces/compare_test_e2e/reference/h100_perf_report.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,3405 +562,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parent op category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent cpu_op</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel stream</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_sum</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_mean</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_max</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Percent of kernels time (%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Percent of total time (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>aten::mm</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6588.415</v>
-      </c>
-      <c r="F2" t="n">
-        <v>96</v>
-      </c>
-      <c r="G2" t="n">
-        <v>68.62932291666667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.392</v>
-      </c>
-      <c r="I2" t="n">
-        <v>86.01600000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14.50148305081948</v>
-      </c>
-      <c r="K2" t="n">
-        <v>18.88208154993822</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3935.211</v>
-      </c>
-      <c r="F3" t="n">
-        <v>73</v>
-      </c>
-      <c r="G3" t="n">
-        <v>53.907</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30.976</v>
-      </c>
-      <c r="I3" t="n">
-        <v>85.504</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8.661627359220446</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.27812607709349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3913.711</v>
-      </c>
-      <c r="F4" t="n">
-        <v>145</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26.99111034482759</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.392</v>
-      </c>
-      <c r="I4" t="n">
-        <v>32.672</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8.614304613826809</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11.21650810777558</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2766.267</v>
-      </c>
-      <c r="F5" t="n">
-        <v>96</v>
-      </c>
-      <c r="G5" t="n">
-        <v>28.81528125</v>
-      </c>
-      <c r="H5" t="n">
-        <v>26.913</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30.048</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.088713903805581</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.927988610751288</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>aten::_flash_attention_forward</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2722.705</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G6" t="n">
-        <v>113.4460416666667</v>
-      </c>
-      <c r="H6" t="n">
-        <v>109.28</v>
-      </c>
-      <c r="I6" t="n">
-        <v>119.647</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.992831418464297</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.803142007057015</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2266.292</v>
-      </c>
-      <c r="F7" t="n">
-        <v>72</v>
-      </c>
-      <c r="G7" t="n">
-        <v>31.47627777777778</v>
-      </c>
-      <c r="H7" t="n">
-        <v>30.912</v>
-      </c>
-      <c r="I7" t="n">
-        <v>32.256</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.988239967610992</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.495084228903703</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2014.326</v>
-      </c>
-      <c r="F8" t="n">
-        <v>48</v>
-      </c>
-      <c r="G8" t="n">
-        <v>41.965125</v>
-      </c>
-      <c r="H8" t="n">
-        <v>41.376</v>
-      </c>
-      <c r="I8" t="n">
-        <v>42.464</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.433648206408521</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.772961751826632</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1671.096</v>
-      </c>
-      <c r="F9" t="n">
-        <v>48</v>
-      </c>
-      <c r="G9" t="n">
-        <v>34.8145</v>
-      </c>
-      <c r="H9" t="n">
-        <v>34.271</v>
-      </c>
-      <c r="I9" t="n">
-        <v>35.615</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.678179094712799</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.789281025827238</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1667.931</v>
-      </c>
-      <c r="F10" t="n">
-        <v>62</v>
-      </c>
-      <c r="G10" t="n">
-        <v>26.90211290322581</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23.392</v>
-      </c>
-      <c r="I10" t="n">
-        <v>32.575</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.671212746379271</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.78021028755323</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1608.923</v>
-      </c>
-      <c r="F11" t="n">
-        <v>49</v>
-      </c>
-      <c r="G11" t="n">
-        <v>32.83516326530612</v>
-      </c>
-      <c r="H11" t="n">
-        <v>32.256</v>
-      </c>
-      <c r="I11" t="n">
-        <v>33.887</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.541332720324028</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.611096188320142</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1434.264</v>
-      </c>
-      <c r="F12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" t="n">
-        <v>28.68528</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.592</v>
-      </c>
-      <c r="I12" t="n">
-        <v>30.049</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.156898144151598</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.110531867245855</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>aten::pow</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1300.795</v>
-      </c>
-      <c r="F13" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" t="n">
-        <v>26.54683673469387</v>
-      </c>
-      <c r="H13" t="n">
-        <v>26.048</v>
-      </c>
-      <c r="I13" t="n">
-        <v>27.552</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.863125143921675</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.728016111576439</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1227.131</v>
-      </c>
-      <c r="F14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G14" t="n">
-        <v>51.13045833333334</v>
-      </c>
-      <c r="H14" t="n">
-        <v>50.176</v>
-      </c>
-      <c r="I14" t="n">
-        <v>52.095</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.700986412913449</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.516898618932966</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1152.541</v>
-      </c>
-      <c r="F15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G15" t="n">
-        <v>28.813525</v>
-      </c>
-      <c r="H15" t="n">
-        <v>27.072</v>
-      </c>
-      <c r="I15" t="n">
-        <v>30.015</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.536809502266407</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.303127254680731</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1132.763</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>113.2763</v>
-      </c>
-      <c r="H16" t="n">
-        <v>111.232</v>
-      </c>
-      <c r="I16" t="n">
-        <v>117.087</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.493276978620112</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.246444454812374</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>aten::silu</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>925.115</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24</v>
-      </c>
-      <c r="G17" t="n">
-        <v>38.54645833333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>38.144</v>
-      </c>
-      <c r="I17" t="n">
-        <v>39.264</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.036231702550441</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.651335241187918</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" t="n">
-        <v>901.4019999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>51</v>
-      </c>
-      <c r="G18" t="n">
-        <v>17.67454901960784</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.471</v>
-      </c>
-      <c r="I18" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.984038015968147</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.583374919958353</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" t="n">
-        <v>854.619</v>
-      </c>
-      <c r="F19" t="n">
-        <v>48</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17.8045625</v>
-      </c>
-      <c r="H19" t="n">
-        <v>17.056</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19.008</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.881065923049519</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.449297084674638</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>835.644</v>
-      </c>
-      <c r="F20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G20" t="n">
-        <v>41.7822</v>
-      </c>
-      <c r="H20" t="n">
-        <v>41.152</v>
-      </c>
-      <c r="I20" t="n">
-        <v>42.463</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.839300848917227</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.394915644311504</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>aten::mean</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" t="n">
-        <v>743.327</v>
-      </c>
-      <c r="F21" t="n">
-        <v>49</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15.1699387755102</v>
-      </c>
-      <c r="H21" t="n">
-        <v>14.176</v>
-      </c>
-      <c r="I21" t="n">
-        <v>16.449</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.636105784428651</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.130339547868634</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>693.72</v>
-      </c>
-      <c r="F22" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.686</v>
-      </c>
-      <c r="H22" t="n">
-        <v>33.92</v>
-      </c>
-      <c r="I22" t="n">
-        <v>35.488</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.526917903929016</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.988168263963813</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" t="n">
-        <v>688.38</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21</v>
-      </c>
-      <c r="G23" t="n">
-        <v>32.78</v>
-      </c>
-      <c r="H23" t="n">
-        <v>32.159</v>
-      </c>
-      <c r="I23" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.515164254607992</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.97286407995648</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" t="n">
-        <v>614.27</v>
-      </c>
-      <c r="F24" t="n">
-        <v>21</v>
-      </c>
-      <c r="G24" t="n">
-        <v>29.25095238095238</v>
-      </c>
-      <c r="H24" t="n">
-        <v>28.736</v>
-      </c>
-      <c r="I24" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.352043851765088</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.760468372693668</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>aten::neg</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>587.328</v>
-      </c>
-      <c r="F25" t="n">
-        <v>48</v>
-      </c>
-      <c r="G25" t="n">
-        <v>12.236</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11.616</v>
-      </c>
-      <c r="I25" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.292742949142047</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.683253892258171</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>563.422</v>
-      </c>
-      <c r="F26" t="n">
-        <v>11</v>
-      </c>
-      <c r="G26" t="n">
-        <v>51.22018181818182</v>
-      </c>
-      <c r="H26" t="n">
-        <v>50.272</v>
-      </c>
-      <c r="I26" t="n">
-        <v>51.904</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.240124458380174</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.614740442280775</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>557.15</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21</v>
-      </c>
-      <c r="G27" t="n">
-        <v>26.53095238095238</v>
-      </c>
-      <c r="H27" t="n">
-        <v>26.048</v>
-      </c>
-      <c r="I27" t="n">
-        <v>27.328</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.226319423072783</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.596765190952312</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>424.928</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11</v>
-      </c>
-      <c r="G28" t="n">
-        <v>38.62981818181818</v>
-      </c>
-      <c r="H28" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I28" t="n">
-        <v>39.232</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.9352911420756919</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1.217823277503337</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>403.868</v>
-      </c>
-      <c r="F29" t="n">
-        <v>22</v>
-      </c>
-      <c r="G29" t="n">
-        <v>18.35763636363636</v>
-      </c>
-      <c r="H29" t="n">
-        <v>17.984</v>
-      </c>
-      <c r="I29" t="n">
-        <v>19.648</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.8889368621691806</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.157466327092396</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>374.208</v>
-      </c>
-      <c r="F30" t="n">
-        <v>21</v>
-      </c>
-      <c r="G30" t="n">
-        <v>17.81942857142857</v>
-      </c>
-      <c r="H30" t="n">
-        <v>17.248</v>
-      </c>
-      <c r="I30" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.8236534841052143</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.072462188954291</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" t="n">
-        <v>314.141</v>
-      </c>
-      <c r="F31" t="n">
-        <v>21</v>
-      </c>
-      <c r="G31" t="n">
-        <v>14.95909523809524</v>
-      </c>
-      <c r="H31" t="n">
-        <v>14.369</v>
-      </c>
-      <c r="I31" t="n">
-        <v>16.352</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.6914425377070937</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.9003130464882894</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>7</v>
-      </c>
-      <c r="E32" t="n">
-        <v>244.605</v>
-      </c>
-      <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" t="n">
-        <v>12.23025</v>
-      </c>
-      <c r="H32" t="n">
-        <v>11.616</v>
-      </c>
-      <c r="I32" t="n">
-        <v>12.768</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.5383897738144453</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.7010262039538551</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>81.797</v>
-      </c>
-      <c r="F33" t="n">
-        <v>49</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.669326530612245</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.952</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.1800399351145732</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.2344262807580118</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>aten::rsqrt</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" t="n">
-        <v>79.07300000000001</v>
-      </c>
-      <c r="F34" t="n">
-        <v>49</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.613734693877551</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.176</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.1740442533260957</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.2266194273430355</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>aten::index_select</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>7</v>
-      </c>
-      <c r="E35" t="n">
-        <v>51.776</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>51.776</v>
-      </c>
-      <c r="H35" t="n">
-        <v>51.776</v>
-      </c>
-      <c r="I35" t="n">
-        <v>51.776</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.113961975139579</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.1483875339257775</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" t="n">
-        <v>35.359</v>
-      </c>
-      <c r="F36" t="n">
-        <v>21</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.683761904761905</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1.952</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.07782720718016792</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.1013371989354444</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>7</v>
-      </c>
-      <c r="E37" t="n">
-        <v>34.499</v>
-      </c>
-      <c r="F37" t="n">
-        <v>21</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.642809523809524</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.537</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.336</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.07593429736442243</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.09887248016272787</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>aten::all</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.009085967115578301</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.01183065010903912</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>aten::bmm</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="H39" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.007747723897004753</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.01008815125576979</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="H40" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.007606856189786485</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.009904730323846705</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3.136</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.006902517653695144</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.00898762566423127</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>aten::cos</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.004578200484593718</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.005961180287500332</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>aten::sin</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.004437332777375449</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.005777759355577245</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>aten::eq</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>7</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.004085163509329779</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.005319207025769527</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>aten::arange</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>7</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.003310391119629303</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.004310391900192548</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>bin_start</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bin_end</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1.471</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1.49757</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1.49757</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1.52414</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1.52414</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1.55071</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1.55071</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.57728</v>
-      </c>
-      <c r="C5" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1.57728</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1.60385</v>
-      </c>
-      <c r="C6" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1.60385</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1.63042</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1.63042</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.65699</v>
-      </c>
-      <c r="C8" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1.65699</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1.68356</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1.68356</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1.71013</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1.71013</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1.7367</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1.7367</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1.76327</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1.76327</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1.78984</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1.78984</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1.81641</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1.81641</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1.84298</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1.84298</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1.86955</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1.86955</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1.89612</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1.89612</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1.92269</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1.92269</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1.94926</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1.94926</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1.97583</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1.97583</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2.0024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2.0024</v>
-      </c>
-      <c r="B22" t="n">
-        <v>2.02897</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2.02897</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2.05554</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2.05554</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2.08211</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2.08211</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2.10868</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2.10868</v>
-      </c>
-      <c r="B26" t="n">
-        <v>2.13525</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2.13525</v>
-      </c>
-      <c r="B27" t="n">
-        <v>2.16182</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2.16182</v>
-      </c>
-      <c r="B28" t="n">
-        <v>2.18839</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2.18839</v>
-      </c>
-      <c r="B29" t="n">
-        <v>2.21496</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2.21496</v>
-      </c>
-      <c r="B30" t="n">
-        <v>2.24153</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2.24153</v>
-      </c>
-      <c r="B31" t="n">
-        <v>2.2681</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2.2681</v>
-      </c>
-      <c r="B32" t="n">
-        <v>2.29467</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2.29467</v>
-      </c>
-      <c r="B33" t="n">
-        <v>2.32124</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2.32124</v>
-      </c>
-      <c r="B34" t="n">
-        <v>2.34781</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2.34781</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2.37438</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2.37438</v>
-      </c>
-      <c r="B36" t="n">
-        <v>2.40095</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2.40095</v>
-      </c>
-      <c r="B37" t="n">
-        <v>2.42752</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2.42752</v>
-      </c>
-      <c r="B38" t="n">
-        <v>2.45409</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2.45409</v>
-      </c>
-      <c r="B39" t="n">
-        <v>2.48066</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2.48066</v>
-      </c>
-      <c r="B40" t="n">
-        <v>2.50723</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2.50723</v>
-      </c>
-      <c r="B41" t="n">
-        <v>2.5338</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2.5338</v>
-      </c>
-      <c r="B42" t="n">
-        <v>2.56037</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2.56037</v>
-      </c>
-      <c r="B43" t="n">
-        <v>2.58694</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2.58694</v>
-      </c>
-      <c r="B44" t="n">
-        <v>2.61351</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2.61351</v>
-      </c>
-      <c r="B45" t="n">
-        <v>2.64008</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2.64008</v>
-      </c>
-      <c r="B46" t="n">
-        <v>2.66665</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2.66665</v>
-      </c>
-      <c r="B47" t="n">
-        <v>2.69322</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2.69322</v>
-      </c>
-      <c r="B48" t="n">
-        <v>2.71979</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2.71979</v>
-      </c>
-      <c r="B49" t="n">
-        <v>2.74636</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2.74636</v>
-      </c>
-      <c r="B50" t="n">
-        <v>2.77293</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2.77293</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2.7995</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2.7995</v>
-      </c>
-      <c r="B52" t="n">
-        <v>2.82607</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2.82607</v>
-      </c>
-      <c r="B53" t="n">
-        <v>2.85264</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2.85264</v>
-      </c>
-      <c r="B54" t="n">
-        <v>2.87921</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2.87921</v>
-      </c>
-      <c r="B55" t="n">
-        <v>2.90578</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2.90578</v>
-      </c>
-      <c r="B56" t="n">
-        <v>2.93235</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2.93235</v>
-      </c>
-      <c r="B57" t="n">
-        <v>2.95892</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2.95892</v>
-      </c>
-      <c r="B58" t="n">
-        <v>2.98549</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>2.98549</v>
-      </c>
-      <c r="B59" t="n">
-        <v>3.01206</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>3.01206</v>
-      </c>
-      <c r="B60" t="n">
-        <v>3.03863</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>3.03863</v>
-      </c>
-      <c r="B61" t="n">
-        <v>3.0652</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>3.0652</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3.09177</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>3.09177</v>
-      </c>
-      <c r="B63" t="n">
-        <v>3.11834</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>3.11834</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3.14491</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>3.14491</v>
-      </c>
-      <c r="B65" t="n">
-        <v>3.17148</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3.17148</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3.19805</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>3.19805</v>
-      </c>
-      <c r="B67" t="n">
-        <v>3.22462</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3.22462</v>
-      </c>
-      <c r="B68" t="n">
-        <v>3.25119</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>3.25119</v>
-      </c>
-      <c r="B69" t="n">
-        <v>3.27776</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>3.27776</v>
-      </c>
-      <c r="B70" t="n">
-        <v>3.30433</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>3.30433</v>
-      </c>
-      <c r="B71" t="n">
-        <v>3.3309</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3.3309</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3.35747</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>3.35747</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3.38404</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>3.38404</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3.41061</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>3.41061</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3.43718</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>3.43718</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3.46375</v>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3.46375</v>
-      </c>
-      <c r="B77" t="n">
-        <v>3.49032</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3.49032</v>
-      </c>
-      <c r="B78" t="n">
-        <v>3.51689</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>3.51689</v>
-      </c>
-      <c r="B79" t="n">
-        <v>3.54346</v>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>3.54346</v>
-      </c>
-      <c r="B80" t="n">
-        <v>3.57003</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>3.57003</v>
-      </c>
-      <c r="B81" t="n">
-        <v>3.5966</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>3.5966</v>
-      </c>
-      <c r="B82" t="n">
-        <v>3.62317</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>3.62317</v>
-      </c>
-      <c r="B83" t="n">
-        <v>3.64974</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>3.64974</v>
-      </c>
-      <c r="B84" t="n">
-        <v>3.67631</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>3.67631</v>
-      </c>
-      <c r="B85" t="n">
-        <v>3.70288</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>3.70288</v>
-      </c>
-      <c r="B86" t="n">
-        <v>3.72945</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>3.72945</v>
-      </c>
-      <c r="B87" t="n">
-        <v>3.75602</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>3.75602</v>
-      </c>
-      <c r="B88" t="n">
-        <v>3.78259</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>3.78259</v>
-      </c>
-      <c r="B89" t="n">
-        <v>3.80916</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>3.80916</v>
-      </c>
-      <c r="B90" t="n">
-        <v>3.83573</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>3.83573</v>
-      </c>
-      <c r="B91" t="n">
-        <v>3.8623</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>3.8623</v>
-      </c>
-      <c r="B92" t="n">
-        <v>3.88887</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>3.88887</v>
-      </c>
-      <c r="B93" t="n">
-        <v>3.91544</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>3.91544</v>
-      </c>
-      <c r="B94" t="n">
-        <v>3.94201</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>3.94201</v>
-      </c>
-      <c r="B95" t="n">
-        <v>3.96858</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>3.96858</v>
-      </c>
-      <c r="B96" t="n">
-        <v>3.99515</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>3.99515</v>
-      </c>
-      <c r="B97" t="n">
-        <v>4.02172</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>4.02172</v>
-      </c>
-      <c r="B98" t="n">
-        <v>4.04829</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>4.04829</v>
-      </c>
-      <c r="B99" t="n">
-        <v>4.07486</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>4.07486</v>
-      </c>
-      <c r="B100" t="n">
-        <v>4.101430000000001</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>4.101430000000001</v>
-      </c>
-      <c r="B101" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parent cpu_op</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Input dims</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Input strides</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) sum</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) mean</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) percent of total time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>((16, 559, 1), (), ())</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>((559, 1, 1), (), ())</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>('', '', '1')</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>81.797</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.669326530612245</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2344262807580118</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aten::rsqrt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>((16, 559, 1),)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>((559, 1, 1),)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>79.07300000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.613734693877551</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.2266194273430355</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>aten::all</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>((16, 559),)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>((559, 1),)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.01183065010903912</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>aten::bmm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>((1, 32, 1), (1, 1, 559))</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>((32, 1, 1), (559, 559, 1))</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>('', '')</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.01008815125576979</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(((1, 559, 32), (1, 559, 32)), ())</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(((17888, 1, 559), (17888, 1, 559)), ())</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>('', '-1')</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.009904730323846705</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>((1, 559, 64), ())</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1), ())</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>('', '')</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3.136</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.568</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.00898762566423127</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>((1, 559, 64), (1, 559, 64), ())</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1), (35776, 64, 1), ())</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>('', '', 'False')</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.4875</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.008526207382362254</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>((1, 1, 559), (1, 1, 559), ())</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>((559, 559, 1), (559, 559, 1), ())</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>('', '', 'False')</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.592</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.592</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.007428547742885029</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>aten::cos</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>((1, 559, 64),)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1),)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.005961180287500332</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aten::sin</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>((1, 559, 64),)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1),)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.016</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.005777759355577245</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>aten::eq</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>((16, 559), ())</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>((559, 1), ())</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>('', '1')</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.005319207025769527</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>aten::arange</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>((), (), (), (0,))</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>((), (), (), (1,))</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>('0', '559', '1', '')</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.504</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.004310391900192548</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4087,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4103,25 +701,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -4137,20 +745,26 @@
         <v>6752.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>220</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>6752.89990234375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.75289990234375</v>
       </c>
       <c r="E2" t="n">
         <v>6.75289990234375</v>
       </c>
       <c r="F2" t="n">
+        <v>220</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>21.16532719371875</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>21.16532719371875</v>
       </c>
     </row>
@@ -4164,20 +778,26 @@
         <v>6668.681640625</v>
       </c>
       <c r="C3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>6668.681640625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.668681640625</v>
       </c>
       <c r="E3" t="n">
         <v>6.668681640625</v>
       </c>
       <c r="F3" t="n">
+        <v>96</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>20.90136547493998</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>42.06669266865873</v>
       </c>
     </row>
@@ -4191,20 +811,26 @@
         <v>5101.934814453125</v>
       </c>
       <c r="C4" t="n">
-        <v>197</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>5101.934814453125</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.101934814453125</v>
       </c>
       <c r="E4" t="n">
         <v>5.101934814453125</v>
       </c>
       <c r="F4" t="n">
+        <v>197</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>15.99077747790201</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>58.05747014656075</v>
       </c>
     </row>
@@ -4218,20 +844,26 @@
         <v>2722.704345703125</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2722.704345703125</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.722704345703125</v>
       </c>
       <c r="E5" t="n">
         <v>2.722704345703125</v>
       </c>
       <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>8.53365652711153</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>66.59112667367228</v>
       </c>
     </row>
@@ -4245,20 +877,26 @@
         <v>2607.51513671875</v>
       </c>
       <c r="C6" t="n">
-        <v>145</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2607.51513671875</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.60751513671875</v>
       </c>
       <c r="E6" t="n">
         <v>2.60751513671875</v>
       </c>
       <c r="F6" t="n">
+        <v>145</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>8.17262388445474</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>74.76375055812701</v>
       </c>
     </row>
@@ -4272,20 +910,26 @@
         <v>2329.075927734375</v>
       </c>
       <c r="C7" t="n">
-        <v>72</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>2329.075927734375</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.329075927734375</v>
       </c>
       <c r="E7" t="n">
         <v>2.329075927734375</v>
       </c>
       <c r="F7" t="n">
+        <v>72</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>7.29992370424488</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>82.06367426237189</v>
       </c>
     </row>
@@ -4299,20 +943,26 @@
         <v>2017.782958984375</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2017.782958984375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.017782958984375</v>
       </c>
       <c r="E8" t="n">
         <v>2.017782958984375</v>
       </c>
       <c r="F8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>6.324251380949954</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>88.38792564332185</v>
       </c>
     </row>
@@ -4326,20 +976,26 @@
         <v>1300.794921875</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1300.794921875</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.300794921875</v>
       </c>
       <c r="E9" t="n">
         <v>1.300794921875</v>
       </c>
       <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>4.077026245251563</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>92.46495188857341</v>
       </c>
     </row>
@@ -4353,20 +1009,26 @@
         <v>925.11474609375</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>925.11474609375</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.92511474609375</v>
       </c>
       <c r="E10" t="n">
         <v>0.92511474609375</v>
       </c>
       <c r="F10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>2.899547835147452</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>95.36449972372085</v>
       </c>
     </row>
@@ -4380,20 +1042,26 @@
         <v>743.327392578125</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>743.327392578125</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.743327392578125</v>
       </c>
       <c r="E11" t="n">
         <v>0.743327392578125</v>
       </c>
       <c r="F11" t="n">
+        <v>49</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>2.329779458230888</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>97.69427918195174</v>
       </c>
     </row>
@@ -4407,20 +1075,26 @@
         <v>587.3271484375</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>587.3271484375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5873271484375</v>
       </c>
       <c r="E12" t="n">
         <v>0.5873271484375</v>
       </c>
       <c r="F12" t="n">
+        <v>48</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>1.840834522383346</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>99.53511370433509</v>
       </c>
     </row>
@@ -4434,20 +1108,26 @@
         <v>79.076416015625</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>79.076416015625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.079076416015625</v>
       </c>
       <c r="E13" t="n">
         <v>0.079076416015625</v>
       </c>
       <c r="F13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>0.2478458502985414</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>99.78295955463363</v>
       </c>
     </row>
@@ -4461,20 +1141,26 @@
         <v>51.77587890625</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>51.77587890625</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.05177587890625</v>
       </c>
       <c r="E14" t="n">
         <v>0.05177587890625</v>
       </c>
       <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>0.1622789369960601</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>99.94523849162969</v>
       </c>
     </row>
@@ -4488,20 +1174,26 @@
         <v>4.1279296875</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>4.1279296875</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0041279296875</v>
       </c>
       <c r="E15" t="n">
         <v>0.0041279296875</v>
       </c>
       <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>0.01293799459966514</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>99.95817648622936</v>
       </c>
     </row>
@@ -4515,20 +1207,26 @@
         <v>3.52001953125</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>3.52001953125</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.00352001953125</v>
       </c>
       <c r="E16" t="n">
         <v>0.00352001953125</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>0.01103264763058741</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>99.96920913385995</v>
       </c>
     </row>
@@ -4542,20 +1240,26 @@
         <v>2.367919921875</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2.367919921875</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.002367919921875</v>
       </c>
       <c r="E17" t="n">
         <v>0.002367919921875</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>0.007421670784371432</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>99.97663080464432</v>
       </c>
     </row>
@@ -4569,20 +1273,26 @@
         <v>2.080078125</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2.080078125</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.002080078125</v>
       </c>
       <c r="E18" t="n">
         <v>0.002080078125</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>0.006519500472506917</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>99.98315030511682</v>
       </c>
     </row>
@@ -4596,20 +1306,26 @@
         <v>2.01611328125</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2.01611328125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.00201611328125</v>
       </c>
       <c r="E19" t="n">
         <v>0.00201611328125</v>
       </c>
       <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>0.006319018180981469</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>99.9894693232978</v>
       </c>
     </row>
@@ -4623,20 +1339,26 @@
         <v>1.85595703125</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1.85595703125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.00185595703125</v>
       </c>
       <c r="E20" t="n">
         <v>0.00185595703125</v>
       </c>
       <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>0.005817047252581877</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>99.99528637055037</v>
       </c>
     </row>
@@ -4650,20 +1372,26 @@
         <v>1.50390625</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>1.50390625</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.00150390625</v>
       </c>
       <c r="E21" t="n">
         <v>0.00150390625</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>0.004713629449605941</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>99.99999999999999</v>
       </c>
     </row>
@@ -4678,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4739,50 +1467,80 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -4841,37 +1599,55 @@
         <v>84.4844258626302</v>
       </c>
       <c r="L2" t="n">
+        <v>84.4844258626302</v>
+      </c>
+      <c r="M2" t="n">
         <v>84.4635009765625</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>84.4635009765625</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.199723729751199</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>1.199723729751199</v>
+      </c>
+      <c r="Q2" t="n">
         <v>82.27197265625</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
+        <v>82.27197265625</v>
+      </c>
+      <c r="S2" t="n">
         <v>86.912109375</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>86.912109375</v>
+      </c>
+      <c r="U2" t="n">
         <v>4055.25244140625</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
+        <v>4055.25244140625</v>
+      </c>
+      <c r="W2" t="n">
         <v>215</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>12.71020539571459</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>12.71020539571459</v>
       </c>
     </row>
@@ -4928,37 +1704,55 @@
         <v>113.4460144042969</v>
       </c>
       <c r="L3" t="n">
+        <v>113.4460144042969</v>
+      </c>
+      <c r="M3" t="n">
         <v>113.7750244140625</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>113.7750244140625</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.173453067400901</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
+        <v>2.173453067400901</v>
+      </c>
+      <c r="Q3" t="n">
         <v>109.280029296875</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
+        <v>109.280029296875</v>
+      </c>
+      <c r="S3" t="n">
         <v>119.64697265625</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>119.64697265625</v>
+      </c>
+      <c r="U3" t="n">
         <v>2722.704345703125</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
+        <v>2722.704345703125</v>
+      </c>
+      <c r="W3" t="n">
         <v>164</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(113.45)}]</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>8.53365652711153</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
         <v>21.24386192282612</v>
       </c>
     </row>
@@ -5015,37 +1809,55 @@
         <v>32.34827677408854</v>
       </c>
       <c r="L4" t="n">
+        <v>32.34827677408854</v>
+      </c>
+      <c r="M4" t="n">
         <v>32.3680419921875</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>32.3680419921875</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.3264361462154342</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>0.3264361462154342</v>
+      </c>
+      <c r="Q4" t="n">
         <v>31.712158203125</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
+        <v>31.712158203125</v>
+      </c>
+      <c r="S4" t="n">
         <v>33.152099609375</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>33.152099609375</v>
+      </c>
+      <c r="U4" t="n">
         <v>2329.075927734375</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>2329.075927734375</v>
+      </c>
+      <c r="W4" t="n">
         <v>89</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}]</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="Z4" t="n">
         <v>7.299923704244882</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
         <v>28.543785627071</v>
       </c>
     </row>
@@ -5102,37 +1914,55 @@
         <v>29.28038533528646</v>
       </c>
       <c r="L5" t="n">
+        <v>29.28038533528646</v>
+      </c>
+      <c r="M5" t="n">
         <v>29.31201171875</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>29.31201171875</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.3233270218510627</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>0.3233270218510627</v>
+      </c>
+      <c r="Q5" t="n">
         <v>28.672119140625</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
+        <v>28.672119140625</v>
+      </c>
+      <c r="S5" t="n">
         <v>30.048095703125</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>30.048095703125</v>
+      </c>
+      <c r="U5" t="n">
         <v>2108.187744140625</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
+        <v>2108.187744140625</v>
+      </c>
+      <c r="W5" t="n">
         <v>145</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(29.28)}]</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="Z5" t="n">
         <v>6.607603257237321</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>35.15138888430833</v>
       </c>
     </row>
@@ -5189,37 +2019,55 @@
         <v>41.96514383951823</v>
       </c>
       <c r="L6" t="n">
+        <v>41.96514383951823</v>
+      </c>
+      <c r="M6" t="n">
         <v>41.9678955078125</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>41.9678955078125</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.2933502450882166</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
+        <v>0.2933502450882166</v>
+      </c>
+      <c r="Q6" t="n">
         <v>41.3759765625</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
+        <v>41.3759765625</v>
+      </c>
+      <c r="S6" t="n">
         <v>42.464111328125</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>42.464111328125</v>
+      </c>
+      <c r="U6" t="n">
         <v>2014.326904296875</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
+        <v>2014.326904296875</v>
+      </c>
+      <c r="W6" t="n">
         <v>129</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(2014.326), 'mean_duration_us': np.float64(41.965125), 'median_duration_us': np.float64(41.968), 'std_dev_duration_us': np.float64(0.290296301575362), 'min_duration_us': np.float64(41.376), 'max_duration_us': np.float64(42.464)}]</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(41.97)}]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
         <v>6.313419215610892</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AA6" t="n">
         <v>41.46480809991922</v>
       </c>
     </row>
@@ -5276,37 +2124,55 @@
         <v>76.47029622395833</v>
       </c>
       <c r="L7" t="n">
+        <v>76.47029622395833</v>
+      </c>
+      <c r="M7" t="n">
         <v>76.4954833984375</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>76.4954833984375</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.4304329398221454</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
+        <v>0.4304329398221454</v>
+      </c>
+      <c r="Q7" t="n">
         <v>75.807861328125</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
+        <v>75.807861328125</v>
+      </c>
+      <c r="S7" t="n">
         <v>77.375</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="U7" t="n">
         <v>1835.287109375</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
+        <v>1835.287109375</v>
+      </c>
+      <c r="W7" t="n">
         <v>235</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}]</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="Z7" t="n">
         <v>5.752262394834891</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AA7" t="n">
         <v>47.21707049475411</v>
       </c>
     </row>
@@ -5363,37 +2229,55 @@
         <v>34.81449890136719</v>
       </c>
       <c r="L8" t="n">
+        <v>34.81449890136719</v>
+      </c>
+      <c r="M8" t="n">
         <v>34.783935546875</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>34.783935546875</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.3250576438614337</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
+        <v>0.3250576438614337</v>
+      </c>
+      <c r="Q8" t="n">
         <v>34.27099609375</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
+        <v>34.27099609375</v>
+      </c>
+      <c r="S8" t="n">
         <v>35.614990234375</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>35.614990234375</v>
+      </c>
+      <c r="U8" t="n">
         <v>1671.095947265625</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
+        <v>1671.095947265625</v>
+      </c>
+      <c r="W8" t="n">
         <v>131</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(34.81)}]</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="Z8" t="n">
         <v>5.237645012877888</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AA8" t="n">
         <v>52.454715507632</v>
       </c>
     </row>
@@ -5450,37 +2334,55 @@
         <v>32.83514528858419</v>
       </c>
       <c r="L9" t="n">
+        <v>32.83514528858419</v>
+      </c>
+      <c r="M9" t="n">
         <v>32.639892578125</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>32.639892578125</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.4306580406298848</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>0.4306580406298848</v>
+      </c>
+      <c r="Q9" t="n">
         <v>32.256103515625</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
+        <v>32.256103515625</v>
+      </c>
+      <c r="S9" t="n">
         <v>33.886962890625</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>33.886962890625</v>
+      </c>
+      <c r="U9" t="n">
         <v>1608.922119140625</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
+        <v>1608.922119140625</v>
+      </c>
+      <c r="W9" t="n">
         <v>77</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.84)}]</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
         <v>5.042776225515153</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AA9" t="n">
         <v>57.49749173314716</v>
       </c>
     </row>
@@ -5537,37 +2439,55 @@
         <v>32.03850809733073</v>
       </c>
       <c r="L10" t="n">
+        <v>32.03850809733073</v>
+      </c>
+      <c r="M10" t="n">
         <v>32</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>32</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.3186166119751925</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>0.3186166119751925</v>
+      </c>
+      <c r="Q10" t="n">
         <v>31.552001953125</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
+        <v>31.552001953125</v>
+      </c>
+      <c r="S10" t="n">
         <v>32.672119140625</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>32.672119140625</v>
+      </c>
+      <c r="U10" t="n">
         <v>1537.848388671875</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
+        <v>1537.848388671875</v>
+      </c>
+      <c r="W10" t="n">
         <v>123</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.04)}]</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="Z10" t="n">
         <v>4.820012852445286</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AA10" t="n">
         <v>62.31750458559245</v>
       </c>
     </row>
@@ -5624,37 +2544,55 @@
         <v>29.21780333227041</v>
       </c>
       <c r="L11" t="n">
+        <v>29.21780333227041</v>
+      </c>
+      <c r="M11" t="n">
         <v>29.216064453125</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>29.216064453125</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.6723608131569377</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
+        <v>0.6723608131569377</v>
+      </c>
+      <c r="Q11" t="n">
         <v>25.2470703125</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
+        <v>25.2470703125</v>
+      </c>
+      <c r="S11" t="n">
         <v>30.049072265625</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>30.049072265625</v>
+      </c>
+      <c r="U11" t="n">
         <v>1431.67236328125</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
+        <v>1431.67236328125</v>
+      </c>
+      <c r="W11" t="n">
         <v>70</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(29.22)}]</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="Z11" t="n">
         <v>4.48722984810352</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AA11" t="n">
         <v>66.80473443369597</v>
       </c>
     </row>
@@ -5711,37 +2649,55 @@
         <v>26.54683514030612</v>
       </c>
       <c r="L12" t="n">
+        <v>26.54683514030612</v>
+      </c>
+      <c r="M12" t="n">
         <v>26.39990234375</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>26.39990234375</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.4194831695891557</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>0.4194831695891557</v>
+      </c>
+      <c r="Q12" t="n">
         <v>26.048095703125</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
+        <v>26.048095703125</v>
+      </c>
+      <c r="S12" t="n">
         <v>27.552001953125</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>27.552001953125</v>
+      </c>
+      <c r="U12" t="n">
         <v>1300.794921875</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
+        <v>1300.794921875</v>
+      </c>
+      <c r="W12" t="n">
         <v>71</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(26.55)}]</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="Z12" t="n">
         <v>4.077026245251564</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AA12" t="n">
         <v>70.88176067894753</v>
       </c>
     </row>
@@ -5798,37 +2754,55 @@
         <v>25.18325494260204</v>
       </c>
       <c r="L13" t="n">
+        <v>25.18325494260204</v>
+      </c>
+      <c r="M13" t="n">
         <v>25.087890625</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>25.087890625</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.3972371439579201</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>0.3972371439579201</v>
+      </c>
+      <c r="Q13" t="n">
         <v>24.575927734375</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
+        <v>24.575927734375</v>
+      </c>
+      <c r="S13" t="n">
         <v>26.14404296875</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
+        <v>26.14404296875</v>
+      </c>
+      <c r="U13" t="n">
         <v>1233.9794921875</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
+        <v>1233.9794921875</v>
+      </c>
+      <c r="W13" t="n">
         <v>82</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(25.18)}]</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="Z13" t="n">
         <v>3.867609483360272</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AA13" t="n">
         <v>74.7493701623078</v>
       </c>
     </row>
@@ -5885,37 +2859,55 @@
         <v>51.13045247395834</v>
       </c>
       <c r="L14" t="n">
+        <v>51.13045247395834</v>
+      </c>
+      <c r="M14" t="n">
         <v>51.0718994140625</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>51.0718994140625</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.6307408003200445</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
+        <v>0.6307408003200445</v>
+      </c>
+      <c r="Q14" t="n">
         <v>50.176025390625</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
+        <v>50.176025390625</v>
+      </c>
+      <c r="S14" t="n">
         <v>52.094970703125</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
+        <v>52.094970703125</v>
+      </c>
+      <c r="U14" t="n">
         <v>1227.130859375</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
+        <v>1227.130859375</v>
+      </c>
+      <c r="W14" t="n">
         <v>227</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(51.13)}]</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="Z14" t="n">
         <v>3.846144104574502</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AA14" t="n">
         <v>78.5955142668823</v>
       </c>
     </row>
@@ -5972,37 +2964,55 @@
         <v>23.78922526041667</v>
       </c>
       <c r="L15" t="n">
+        <v>23.78922526041667</v>
+      </c>
+      <c r="M15" t="n">
         <v>23.77587890625</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>23.77587890625</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.1826717306685092</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
+        <v>0.1826717306685092</v>
+      </c>
+      <c r="Q15" t="n">
         <v>23.39208984375</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
+        <v>23.39208984375</v>
+      </c>
+      <c r="S15" t="n">
         <v>24.35205078125</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
+        <v>24.35205078125</v>
+      </c>
+      <c r="U15" t="n">
         <v>1141.8828125</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="V15" t="n">
+        <v>1141.8828125</v>
+      </c>
+      <c r="W15" t="n">
         <v>130</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(23.79)}]</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="Z15" t="n">
         <v>3.578954773942098</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AA15" t="n">
         <v>82.17446904082441</v>
       </c>
     </row>
@@ -6059,37 +3069,55 @@
         <v>38.54644775390625</v>
       </c>
       <c r="L16" t="n">
+        <v>38.54644775390625</v>
+      </c>
+      <c r="M16" t="n">
         <v>38.4158935546875</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>38.4158935546875</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.3625162870903211</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
+        <v>0.3625162870903211</v>
+      </c>
+      <c r="Q16" t="n">
         <v>38.14404296875</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
+        <v>38.14404296875</v>
+      </c>
+      <c r="S16" t="n">
         <v>39.263916015625</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
+        <v>39.263916015625</v>
+      </c>
+      <c r="U16" t="n">
         <v>925.11474609375</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="V16" t="n">
+        <v>925.11474609375</v>
+      </c>
+      <c r="W16" t="n">
         <v>217</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(38.55)}]</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="Z16" t="n">
         <v>2.899547835147452</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AA16" t="n">
         <v>85.07401687597186</v>
       </c>
     </row>
@@ -6146,37 +3174,55 @@
         <v>18.33525490274235</v>
       </c>
       <c r="L17" t="n">
+        <v>18.33525490274235</v>
+      </c>
+      <c r="M17" t="n">
         <v>18.239990234375</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>18.239990234375</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.3646247760047354</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
+        <v>0.3646247760047354</v>
+      </c>
+      <c r="Q17" t="n">
         <v>17.85498046875</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
+        <v>17.85498046875</v>
+      </c>
+      <c r="S17" t="n">
         <v>19.52001953125</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>19.52001953125</v>
+      </c>
+      <c r="U17" t="n">
         <v>898.427490234375</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="V17" t="n">
+        <v>898.427490234375</v>
+      </c>
+      <c r="W17" t="n">
         <v>81</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(18.34)}]</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="Z17" t="n">
         <v>2.81590310320494</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AA17" t="n">
         <v>87.88991997917681</v>
       </c>
     </row>
@@ -6233,37 +3279,55 @@
         <v>17.80457051595052</v>
       </c>
       <c r="L18" t="n">
+        <v>17.80457051595052</v>
+      </c>
+      <c r="M18" t="n">
         <v>17.85595703125</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>17.85595703125</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.5205274181052388</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
+        <v>0.5205274181052388</v>
+      </c>
+      <c r="Q18" t="n">
         <v>17.055908203125</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
+        <v>17.055908203125</v>
+      </c>
+      <c r="S18" t="n">
         <v>19.008056640625</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>19.008056640625</v>
+      </c>
+      <c r="U18" t="n">
         <v>854.619384765625</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="V18" t="n">
+        <v>854.619384765625</v>
+      </c>
+      <c r="W18" t="n">
         <v>191</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(17.8)}]</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="Z18" t="n">
         <v>2.678597219896759</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
         <v>90.56851719907357</v>
       </c>
     </row>
@@ -6320,37 +3384,55 @@
         <v>32.42258707682291</v>
       </c>
       <c r="L19" t="n">
+        <v>32.42258707682291</v>
+      </c>
+      <c r="M19" t="n">
         <v>32.4000244140625</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>32.4000244140625</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.1504456175239329</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>0.1504456175239329</v>
+      </c>
+      <c r="Q19" t="n">
         <v>32.192138671875</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
+        <v>32.192138671875</v>
+      </c>
+      <c r="S19" t="n">
         <v>32.7041015625</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
+        <v>32.7041015625</v>
+      </c>
+      <c r="U19" t="n">
         <v>778.14208984375</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="V19" t="n">
+        <v>778.14208984375</v>
+      </c>
+      <c r="W19" t="n">
         <v>189</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}]</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="Z19" t="n">
         <v>2.438897684390508</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
         <v>93.00741488346408</v>
       </c>
     </row>
@@ -6407,37 +3489,55 @@
         <v>15.16994678730867</v>
       </c>
       <c r="L20" t="n">
+        <v>15.16994678730867</v>
+      </c>
+      <c r="M20" t="n">
         <v>15.072021484375</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>15.072021484375</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.4689977659830294</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
+        <v>0.4689977659830294</v>
+      </c>
+      <c r="Q20" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
+        <v>14.176025390625</v>
+      </c>
+      <c r="S20" t="n">
         <v>16.448974609375</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>16.448974609375</v>
+      </c>
+      <c r="U20" t="n">
         <v>743.327392578125</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="V20" t="n">
+        <v>743.327392578125</v>
+      </c>
+      <c r="W20" t="n">
         <v>74</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 7, 'mean_duration_us': np.float64(15.17)}]</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="Z20" t="n">
         <v>2.329779458230888</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
         <v>95.33719434169497</v>
       </c>
     </row>
@@ -6494,37 +3594,55 @@
         <v>27.42001342773438</v>
       </c>
       <c r="L21" t="n">
+        <v>27.42001342773438</v>
+      </c>
+      <c r="M21" t="n">
         <v>27.4560546875</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>27.4560546875</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.2265912406627222</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
+        <v>0.2265912406627222</v>
+      </c>
+      <c r="Q21" t="n">
         <v>26.9130859375</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
+        <v>26.9130859375</v>
+      </c>
+      <c r="S21" t="n">
         <v>27.8720703125</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>27.8720703125</v>
+      </c>
+      <c r="U21" t="n">
         <v>658.080322265625</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="V21" t="n">
+        <v>658.080322265625</v>
+      </c>
+      <c r="W21" t="n">
         <v>179</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(27.42)}]</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="Z21" t="n">
         <v>2.062593188396829</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AA21" t="n">
         <v>97.3997875300918</v>
       </c>
     </row>
@@ -6581,37 +3699,55 @@
         <v>12.23598225911458</v>
       </c>
       <c r="L22" t="n">
+        <v>12.23598225911458</v>
+      </c>
+      <c r="M22" t="n">
         <v>12.19189453125</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>12.19189453125</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.339127372422647</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
+        <v>0.339127372422647</v>
+      </c>
+      <c r="Q22" t="n">
         <v>11.615966796875</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
+        <v>11.615966796875</v>
+      </c>
+      <c r="S22" t="n">
         <v>13.280029296875</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
+        <v>13.280029296875</v>
+      </c>
+      <c r="U22" t="n">
         <v>587.3271484375</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="V22" t="n">
+        <v>587.3271484375</v>
+      </c>
+      <c r="W22" t="n">
         <v>128</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(12.24)}]</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="Z22" t="n">
         <v>1.840834522383346</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AA22" t="n">
         <v>99.24062205247515</v>
       </c>
     </row>
@@ -6668,37 +3804,55 @@
         <v>1.669383769132653</v>
       </c>
       <c r="L23" t="n">
+        <v>1.669383769132653</v>
+      </c>
+      <c r="M23" t="n">
         <v>1.632080078125</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>1.632080078125</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.0834552892669608</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
+        <v>0.0834552892669608</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.568115234375</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="S23" t="n">
         <v>1.951904296875</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
+        <v>1.951904296875</v>
+      </c>
+      <c r="U23" t="n">
         <v>81.7998046875</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="V23" t="n">
+        <v>81.7998046875</v>
+      </c>
+      <c r="W23" t="n">
         <v>75</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.67)}]</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="Z23" t="n">
         <v>0.2563816516800925</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AA23" t="n">
         <v>99.49700370415523</v>
       </c>
     </row>
@@ -6755,37 +3909,55 @@
         <v>1.613804408482143</v>
       </c>
       <c r="L24" t="n">
+        <v>1.613804408482143</v>
+      </c>
+      <c r="M24" t="n">
         <v>1.60009765625</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>1.60009765625</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.1026021369823694</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
+        <v>0.1026021369823694</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.535888671875</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
+        <v>1.535888671875</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="P24" t="n">
+      <c r="T24" t="n">
+        <v>2.176025390625</v>
+      </c>
+      <c r="U24" t="n">
         <v>79.076416015625</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="V24" t="n">
+        <v>79.076416015625</v>
+      </c>
+      <c r="W24" t="n">
         <v>76</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="Z24" t="n">
         <v>0.2478458502985415</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AA24" t="n">
         <v>99.74484955445378</v>
       </c>
     </row>
@@ -6844,33 +4016,49 @@
       <c r="L25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>51.77587890625</v>
+      </c>
       <c r="N25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="T25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="U25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="V25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="W25" t="n">
         <v>4</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(51.776), 'mean_duration_us': np.float64(51.776), 'median_duration_us': np.float64(51.776), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.776), 'max_duration_us': np.float64(51.776)}]</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(51.78)}]</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="Z25" t="n">
         <v>0.1622789369960601</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AA25" t="n">
         <v>99.90712849144984</v>
       </c>
     </row>
@@ -6929,33 +4117,49 @@
       <c r="L26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>4.1279296875</v>
+      </c>
       <c r="N26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="W26" t="n">
         <v>15</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(4.128), 'mean_duration_us': np.float64(4.128), 'median_duration_us': np.float64(4.128), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(4.128)}]</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool...', 'stream': 7, 'mean_duration_us': np.float64(4.13)}]</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="Z26" t="n">
         <v>0.01293799459966514</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AA26" t="n">
         <v>99.92006648604951</v>
       </c>
     </row>
@@ -7014,33 +4218,49 @@
       <c r="L27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>3.52001953125</v>
+      </c>
       <c r="N27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="W27" t="n">
         <v>50</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1...', 'stream': 7, 'mean_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="Z27" t="n">
         <v>0.01103264763058741</v>
       </c>
-      <c r="U27" t="n">
+      <c r="AA27" t="n">
         <v>99.93109913368009</v>
       </c>
     </row>
@@ -7099,33 +4319,49 @@
       <c r="L28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>3.4560546875</v>
+      </c>
       <c r="N28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="W28" t="n">
         <v>54</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.456), 'mean_duration_us': np.float64(3.456), 'median_duration_us': np.float64(3.456), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.456), 'max_duration_us': np.float64(3.456)}]</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(3.46)}]</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="Z28" t="n">
         <v>0.01083216533906196</v>
       </c>
-      <c r="U28" t="n">
+      <c r="AA28" t="n">
         <v>99.94193129901916</v>
       </c>
     </row>
@@ -7185,34 +4421,52 @@
         <v>1.568115234375</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.568115234375</v>
       </c>
       <c r="N29" t="n">
         <v>1.568115234375</v>
       </c>
       <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1.568115234375</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="U29" t="n">
         <v>3.13623046875</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="V29" t="n">
+        <v>3.13623046875</v>
+      </c>
+      <c r="W29" t="n">
         <v>57</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="Z29" t="n">
         <v>0.009829753881434726</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AA29" t="n">
         <v>99.95176105290059</v>
       </c>
     </row>
@@ -7272,34 +4526,52 @@
         <v>1.4874267578125</v>
       </c>
       <c r="M30" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.02330552135258396</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
+        <v>0.02330552135258396</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.470947265625</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
+        <v>1.470947265625</v>
+      </c>
+      <c r="S30" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.974853515625</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="V30" t="n">
+        <v>2.974853515625</v>
+      </c>
+      <c r="W30" t="n">
         <v>62</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="Z30" t="n">
         <v>0.009323956955105258</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AA30" t="n">
         <v>99.96108500985569</v>
       </c>
     </row>
@@ -7358,33 +4630,49 @@
       <c r="L31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2.592041015625</v>
+      </c>
       <c r="N31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="W31" t="n">
         <v>38</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.59)}]</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="Z31" t="n">
         <v>0.008124124004296473</v>
       </c>
-      <c r="U31" t="n">
+      <c r="AA31" t="n">
         <v>99.96920913385999</v>
       </c>
     </row>
@@ -7443,33 +4731,49 @@
       <c r="L32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>2.367919921875</v>
+      </c>
       <c r="N32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="W32" t="n">
         <v>19</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.368), 'mean_duration_us': np.float64(2.368), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.368), 'max_duration_us': np.float64(2.368)}]</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'mean_duration_us': np.float64(2.37)}]</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="Z32" t="n">
         <v>0.007421670784371432</v>
       </c>
-      <c r="U32" t="n">
+      <c r="AA32" t="n">
         <v>99.97663080464436</v>
       </c>
     </row>
@@ -7528,33 +4832,49 @@
       <c r="L33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>2.080078125</v>
+      </c>
       <c r="N33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="W33" t="n">
         <v>55</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.08), 'mean_duration_us': np.float64(2.08), 'median_duration_us': np.float64(2.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.08), 'max_duration_us': np.float64(2.08)}]</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': np.float64(2.08)}]</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="Z33" t="n">
         <v>0.006519500472506919</v>
       </c>
-      <c r="U33" t="n">
+      <c r="AA33" t="n">
         <v>99.98315030511687</v>
       </c>
     </row>
@@ -7613,33 +4933,49 @@
       <c r="L34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>2.01611328125</v>
+      </c>
       <c r="N34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="W34" t="n">
         <v>56</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.016), 'mean_duration_us': np.float64(2.016), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.016), 'max_duration_us': np.float64(2.016)}]</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(2.02)}]</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="Z34" t="n">
         <v>0.00631901818098147</v>
       </c>
-      <c r="U34" t="n">
+      <c r="AA34" t="n">
         <v>99.98946932329784</v>
       </c>
     </row>
@@ -7698,33 +5034,49 @@
       <c r="L35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>1.85595703125</v>
+      </c>
       <c r="N35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="W35" t="n">
         <v>14</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.856), 'mean_duration_us': np.float64(1.856), 'median_duration_us': np.float64(1.856), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(1.856)}]</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.86)}]</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="Z35" t="n">
         <v>0.005817047252581877</v>
       </c>
-      <c r="U35" t="n">
+      <c r="AA35" t="n">
         <v>99.99528637055042</v>
       </c>
     </row>
@@ -7783,33 +5135,49 @@
       <c r="L36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>1.50390625</v>
+      </c>
       <c r="N36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="W36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.504), 'mean_duration_us': np.float64(1.504), 'median_duration_us': np.float64(1.504), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.504), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="Z36" t="n">
         <v>0.004713629449605941</v>
       </c>
-      <c r="U36" t="n">
+      <c r="AA36" t="n">
         <v>100</v>
       </c>
     </row>
@@ -8178,12 +5546,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -8488,12 +5856,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -8925,12 +6293,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -10741,12 +8109,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}]</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
